--- a/results/Int Task Remove ACC -0.9/Rando_3_permute.xlsx
+++ b/results/Int Task Remove ACC -0.9/Rando_3_permute.xlsx
@@ -440,853 +440,853 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6984500546592625</v>
+        <v>0.7128193908833697</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6970580724766344</v>
+        <v>0.7138205980300154</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7003937295907097</v>
+        <v>0.7127282921126051</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6970316925237103</v>
+        <v>0.7088094621725545</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.690066681486338</v>
+        <v>0.7125248147423839</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6907307528346138</v>
+        <v>0.7166684018813478</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6872026979305454</v>
+        <v>0.7131676062619677</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6902752589807912</v>
+        <v>0.7141688134086135</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6905536554173168</v>
+        <v>0.7119254622119485</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6954949723327053</v>
+        <v>0.7268294321486507</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6935785566859463</v>
+        <v>0.7245597009990616</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.680724660824152</v>
+        <v>0.7205446721640143</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6796323549067416</v>
+        <v>0.6848137293937394</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.675215471455484</v>
+        <v>0.6412518096647706</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6722280297200067</v>
+        <v>0.6376326559899377</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6804666648845543</v>
+        <v>0.6370494831639623</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6871362204491768</v>
+        <v>0.6370494831639623</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6798877128510468</v>
+        <v>0.6386074831836593</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6776069021212296</v>
+        <v>0.6368996450313534</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6574338003874687</v>
+        <v>0.6543900814190867</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6577623187345502</v>
+        <v>0.6630416507800728</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6577623187345502</v>
+        <v>0.6690761529446358</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6459428687600859</v>
+        <v>0.6537685697281951</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6413599674717594</v>
+        <v>0.654791056703533</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6219573362297349</v>
+        <v>0.6524140470787192</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6225141291027861</v>
+        <v>0.6502132555394384</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6244356448737772</v>
+        <v>0.6480933625224581</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6177328505684704</v>
+        <v>0.6474241910499503</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5861199943159995</v>
+        <v>0.637712675180474</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5677117114328606</v>
+        <v>0.6364423925140025</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5660677127666309</v>
+        <v>0.6350878698645266</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5868605675277552</v>
+        <v>0.6192243731067987</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5829417375877045</v>
+        <v>0.6059788228772579</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5663716098243166</v>
+        <v>0.5591009430657304</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5663716098243166</v>
+        <v>0.5633679883843792</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5672229788383535</v>
+        <v>0.5647599705670072</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5647335906140831</v>
+        <v>0.5713291064441652</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5644713738820176</v>
+        <v>0.563673644105593</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5648246893848476</v>
+        <v>0.563673644105593</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5691504740653407</v>
+        <v>0.5485227578095213</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5691504740653407</v>
+        <v>0.5514565603073862</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5682241859849992</v>
+        <v>0.5514565603073862</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5687060597917462</v>
+        <v>0.5240340716437314</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.575430133925745</v>
+        <v>0.5267805764758353</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5751142779560672</v>
+        <v>0.5212662869829353</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5802701518219051</v>
+        <v>0.52241733226219</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5669071228686757</v>
+        <v>0.52241733226219</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.562468959588726</v>
+        <v>0.52241733226219</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5666236263079181</v>
+        <v>0.5242060689367964</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5758056085890313</v>
+        <v>0.5276217452414083</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5820963480296637</v>
+        <v>0.5293670429268663</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5815770146897647</v>
+        <v>0.5151586244155961</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5791199858744145</v>
+        <v>0.5129476326278514</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5829638967481607</v>
+        <v>0.5124393788681805</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5542234656364181</v>
+        <v>0.4932207038312133</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5502671761632152</v>
+        <v>0.4932207038312133</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5601072503366082</v>
+        <v>0.4932207038312133</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5607015027428116</v>
+        <v>0.506495975474382</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5570448895348264</v>
+        <v>0.5104693239838091</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5438904380760503</v>
+        <v>0.5029032017524731</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5447256273856271</v>
+        <v>0.5013392222767799</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5444472309491015</v>
+        <v>0.5014141413430843</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5444472309491015</v>
+        <v>0.5009322675363375</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5431301678327778</v>
+        <v>0.4997650425526228</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5322565271038189</v>
+        <v>0.500321835425674</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5291567067688849</v>
+        <v>0.4983356008368424</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5177049933381825</v>
+        <v>0.4939936364518893</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5174265969016569</v>
+        <v>0.497227115214972</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5165914075920801</v>
+        <v>0.4995343058977133</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5203016600376776</v>
+        <v>0.4996841440303222</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5203016600376776</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.515012127743691</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5151245063431477</v>
+        <v>0.5002783964365256</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5013170631163236</v>
+        <v>0.5002783964365256</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5013170631163236</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5018363964562226</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5018363964562226</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5024681083955783</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5029874417354774</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5074741441288073</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5105850440439694</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5030572606775497</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5004444142735945</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5004444142735945</v>
+        <v>0.4999625404668478</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5002783964365256</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -1296,17 +1296,17 @@
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5002783964365256</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -1316,11 +1316,11 @@
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.49964668449717</v>
+        <v>0.5002783964365256</v>
       </c>
     </row>
   </sheetData>
